--- a/data/nzd0090/nzd0090.xlsx
+++ b/data/nzd0090/nzd0090.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M308"/>
+  <dimension ref="A1:M309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14306,6 +14306,51 @@
         <v>324.75</v>
       </c>
       <c r="M308" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>309.13</v>
+      </c>
+      <c r="C309" t="n">
+        <v>300.27</v>
+      </c>
+      <c r="D309" t="n">
+        <v>296.42</v>
+      </c>
+      <c r="E309" t="n">
+        <v>297.84</v>
+      </c>
+      <c r="F309" t="n">
+        <v>300.86</v>
+      </c>
+      <c r="G309" t="n">
+        <v>314.17</v>
+      </c>
+      <c r="H309" t="n">
+        <v>321.44</v>
+      </c>
+      <c r="I309" t="n">
+        <v>332.32</v>
+      </c>
+      <c r="J309" t="n">
+        <v>342.73</v>
+      </c>
+      <c r="K309" t="n">
+        <v>342.46</v>
+      </c>
+      <c r="L309" t="n">
+        <v>325.39</v>
+      </c>
+      <c r="M309" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14322,7 +14367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B316"/>
+  <dimension ref="A1:B317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17485,6 +17530,16 @@
       </c>
       <c r="B316" t="n">
         <v>0.14</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>
@@ -17653,28 +17708,28 @@
         <v>0.0819</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1496660899106802</v>
+        <v>0.1475948835033068</v>
       </c>
       <c r="J2" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K2" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06165674640201058</v>
+        <v>0.06035380109806543</v>
       </c>
       <c r="M2" t="n">
-        <v>3.038954811570443</v>
+        <v>3.040237291823281</v>
       </c>
       <c r="N2" t="n">
-        <v>17.77107913472728</v>
+        <v>17.74560185215245</v>
       </c>
       <c r="O2" t="n">
-        <v>4.215575777367462</v>
+        <v>4.212552890131168</v>
       </c>
       <c r="P2" t="n">
-        <v>308.3777316864795</v>
+        <v>308.3998744601585</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17731,28 +17786,28 @@
         <v>0.1027</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1439706014322799</v>
+        <v>0.1421616255250518</v>
       </c>
       <c r="J3" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K3" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05747609376651031</v>
+        <v>0.0564161464726366</v>
       </c>
       <c r="M3" t="n">
-        <v>3.121441650727902</v>
+        <v>3.120514692199876</v>
       </c>
       <c r="N3" t="n">
-        <v>17.71897562441047</v>
+        <v>17.68602514113937</v>
       </c>
       <c r="O3" t="n">
-        <v>4.209391360328767</v>
+        <v>4.205475614141564</v>
       </c>
       <c r="P3" t="n">
-        <v>299.2657122041857</v>
+        <v>299.2850515341347</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17809,28 +17864,28 @@
         <v>0.1427</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09213862068448314</v>
+        <v>0.09011442742665579</v>
       </c>
       <c r="J4" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K4" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0176699741188171</v>
+        <v>0.017009951839005</v>
       </c>
       <c r="M4" t="n">
-        <v>3.644231321594141</v>
+        <v>3.641484644921546</v>
       </c>
       <c r="N4" t="n">
-        <v>24.60315267543087</v>
+        <v>24.55404720287837</v>
       </c>
       <c r="O4" t="n">
-        <v>4.960156517231172</v>
+        <v>4.955204052597468</v>
       </c>
       <c r="P4" t="n">
-        <v>297.0975027641508</v>
+        <v>297.1191429314616</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17887,28 +17942,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1176237749741056</v>
+        <v>0.1151230219485849</v>
       </c>
       <c r="J5" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K5" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02878972264439661</v>
+        <v>0.02774676083709893</v>
       </c>
       <c r="M5" t="n">
-        <v>3.791499940245673</v>
+        <v>3.789281458827617</v>
       </c>
       <c r="N5" t="n">
-        <v>24.33054618153323</v>
+        <v>24.29852237837322</v>
       </c>
       <c r="O5" t="n">
-        <v>4.93260034682856</v>
+        <v>4.929353139953885</v>
       </c>
       <c r="P5" t="n">
-        <v>298.5860576661501</v>
+        <v>298.6127926202687</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17965,28 +18020,28 @@
         <v>0.0916</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09733725217017557</v>
+        <v>0.09287423340581737</v>
       </c>
       <c r="J6" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K6" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02119125784321674</v>
+        <v>0.01933651193083696</v>
       </c>
       <c r="M6" t="n">
-        <v>3.816076172010487</v>
+        <v>3.823818594596659</v>
       </c>
       <c r="N6" t="n">
-        <v>22.81314236585668</v>
+        <v>22.8886800737882</v>
       </c>
       <c r="O6" t="n">
-        <v>4.776310539093608</v>
+        <v>4.784211541496489</v>
       </c>
       <c r="P6" t="n">
-        <v>305.1358554215997</v>
+        <v>305.1835684906944</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18043,28 +18098,28 @@
         <v>0.1115</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09243201555619383</v>
+        <v>0.09038083149206187</v>
       </c>
       <c r="J7" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K7" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02304643223767289</v>
+        <v>0.02217107225480996</v>
       </c>
       <c r="M7" t="n">
-        <v>3.414742310104303</v>
+        <v>3.413418958100146</v>
       </c>
       <c r="N7" t="n">
-        <v>18.87995305006678</v>
+        <v>18.85025557754842</v>
       </c>
       <c r="O7" t="n">
-        <v>4.345106793862124</v>
+        <v>4.341688102287914</v>
       </c>
       <c r="P7" t="n">
-        <v>314.8844124788573</v>
+        <v>314.9063411984405</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18121,28 +18176,28 @@
         <v>0.0945</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05728418933893006</v>
+        <v>0.05871398841508267</v>
       </c>
       <c r="J8" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K8" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008779719057103064</v>
+        <v>0.009275674622765018</v>
       </c>
       <c r="M8" t="n">
-        <v>3.411291206536598</v>
+        <v>3.406624507763757</v>
       </c>
       <c r="N8" t="n">
-        <v>19.31278680547928</v>
+        <v>19.26543769804213</v>
       </c>
       <c r="O8" t="n">
-        <v>4.394631589277909</v>
+        <v>4.389241130086399</v>
       </c>
       <c r="P8" t="n">
-        <v>317.7493122789257</v>
+        <v>317.734026638037</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18199,28 +18254,28 @@
         <v>0.0588</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1482049524006723</v>
+        <v>0.1516081105170998</v>
       </c>
       <c r="J9" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K9" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L9" t="n">
-        <v>0.046820815030579</v>
+        <v>0.04903867126502837</v>
       </c>
       <c r="M9" t="n">
-        <v>3.473235925418428</v>
+        <v>3.482044312836493</v>
       </c>
       <c r="N9" t="n">
-        <v>23.31024595544046</v>
+        <v>23.32155084136559</v>
       </c>
       <c r="O9" t="n">
-        <v>4.828068553307882</v>
+        <v>4.829239157607086</v>
       </c>
       <c r="P9" t="n">
-        <v>323.2308097675609</v>
+        <v>323.1944274158562</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18277,28 +18332,28 @@
         <v>0.0578</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04178670036187079</v>
+        <v>0.04443285990184843</v>
       </c>
       <c r="J10" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K10" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L10" t="n">
-        <v>0.003778016853624666</v>
+        <v>0.004289773421491838</v>
       </c>
       <c r="M10" t="n">
-        <v>3.371515133372872</v>
+        <v>3.376110159467897</v>
       </c>
       <c r="N10" t="n">
-        <v>24.00237578182229</v>
+        <v>23.97703859222204</v>
       </c>
       <c r="O10" t="n">
-        <v>4.89922195678276</v>
+        <v>4.896635435911279</v>
       </c>
       <c r="P10" t="n">
-        <v>337.5929176232825</v>
+        <v>337.5646281628001</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18355,28 +18410,28 @@
         <v>0.0639</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0007559385821302746</v>
+        <v>0.002271656539345206</v>
       </c>
       <c r="J11" t="n">
+        <v>308</v>
+      </c>
+      <c r="K11" t="n">
         <v>307</v>
       </c>
-      <c r="K11" t="n">
-        <v>306</v>
-      </c>
       <c r="L11" t="n">
-        <v>1.798470648739503e-06</v>
+        <v>1.633737298789573e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>2.984790902445389</v>
+        <v>2.982029123125597</v>
       </c>
       <c r="N11" t="n">
-        <v>16.6017647287668</v>
+        <v>16.56492471225877</v>
       </c>
       <c r="O11" t="n">
-        <v>4.074526319557502</v>
+        <v>4.070003035902894</v>
       </c>
       <c r="P11" t="n">
-        <v>340.1279945714015</v>
+        <v>340.111817950189</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -18433,28 +18488,28 @@
         <v>0.0709</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0922520447023774</v>
+        <v>0.08806487808954415</v>
       </c>
       <c r="J12" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K12" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01714067104870765</v>
+        <v>0.01567095753665215</v>
       </c>
       <c r="M12" t="n">
-        <v>3.951865709590933</v>
+        <v>3.957417835999941</v>
       </c>
       <c r="N12" t="n">
-        <v>25.43907925819046</v>
+        <v>25.48816886995258</v>
       </c>
       <c r="O12" t="n">
-        <v>5.043716809872503</v>
+        <v>5.048580876835844</v>
       </c>
       <c r="P12" t="n">
-        <v>329.3787870290017</v>
+        <v>329.4235510285406</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -18492,7 +18547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M308"/>
+  <dimension ref="A1:M309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39127,6 +39182,73 @@
         </is>
       </c>
     </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>-35.55974726978788,174.48614754817334</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>-35.5601145821756,174.4869315356577</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>-35.56044037816611,174.48773728384293</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>-35.56072250300331,174.48856592141405</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>-35.560992113019076,174.48940364066826</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>-35.561179536042246,174.49031250198558</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>-35.56134349326982,174.49121833979672</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>-35.561469274172865,174.49211012889512</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>-35.561604239948274,174.4930251531905</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>-35.56165936360306,174.4939467765842</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>-35.56182805013528,174.49484825214668</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0090/nzd0090.xlsx
+++ b/data/nzd0090/nzd0090.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M309"/>
+  <dimension ref="A1:M310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14351,6 +14351,51 @@
         <v>325.39</v>
       </c>
       <c r="M309" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>311.24</v>
+      </c>
+      <c r="C310" t="n">
+        <v>301.97</v>
+      </c>
+      <c r="D310" t="n">
+        <v>296.3</v>
+      </c>
+      <c r="E310" t="n">
+        <v>297.3</v>
+      </c>
+      <c r="F310" t="n">
+        <v>301.05</v>
+      </c>
+      <c r="G310" t="n">
+        <v>314.34</v>
+      </c>
+      <c r="H310" t="n">
+        <v>322.18</v>
+      </c>
+      <c r="I310" t="n">
+        <v>333.4</v>
+      </c>
+      <c r="J310" t="n">
+        <v>343.93</v>
+      </c>
+      <c r="K310" t="n">
+        <v>342.86</v>
+      </c>
+      <c r="L310" t="n">
+        <v>325.99</v>
+      </c>
+      <c r="M310" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14367,7 +14412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B317"/>
+  <dimension ref="A1:B318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17540,6 +17585,16 @@
       </c>
       <c r="B317" t="n">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>0.72</v>
       </c>
     </row>
   </sheetData>
@@ -17708,28 +17763,28 @@
         <v>0.0819</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1475948835033068</v>
+        <v>0.146919054532744</v>
       </c>
       <c r="J2" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K2" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06035380109806543</v>
+        <v>0.0602173102808099</v>
       </c>
       <c r="M2" t="n">
-        <v>3.040237291823281</v>
+        <v>3.033996425064482</v>
       </c>
       <c r="N2" t="n">
-        <v>17.74560185215245</v>
+        <v>17.69160536319646</v>
       </c>
       <c r="O2" t="n">
-        <v>4.212552890131168</v>
+        <v>4.206139009019608</v>
       </c>
       <c r="P2" t="n">
-        <v>308.3998744601585</v>
+        <v>308.407127235697</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17786,28 +17841,28 @@
         <v>0.1027</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1421616255250518</v>
+        <v>0.1414740191421134</v>
       </c>
       <c r="J3" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K3" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0564161464726366</v>
+        <v>0.05626011236616957</v>
       </c>
       <c r="M3" t="n">
-        <v>3.120514692199876</v>
+        <v>3.113906703563941</v>
       </c>
       <c r="N3" t="n">
-        <v>17.68602514113937</v>
+        <v>17.63234213823831</v>
       </c>
       <c r="O3" t="n">
-        <v>4.205475614141564</v>
+        <v>4.19908825082759</v>
       </c>
       <c r="P3" t="n">
-        <v>299.2850515341347</v>
+        <v>299.2924307010119</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17864,28 +17919,28 @@
         <v>0.1427</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09011442742665579</v>
+        <v>0.08803221354728159</v>
       </c>
       <c r="J4" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K4" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L4" t="n">
-        <v>0.017009951839005</v>
+        <v>0.01633585451113029</v>
       </c>
       <c r="M4" t="n">
-        <v>3.641484644921546</v>
+        <v>3.6389414353756</v>
       </c>
       <c r="N4" t="n">
-        <v>24.55404720287837</v>
+        <v>24.50716836733871</v>
       </c>
       <c r="O4" t="n">
-        <v>4.955204052597468</v>
+        <v>4.950471529797815</v>
       </c>
       <c r="P4" t="n">
-        <v>297.1191429314616</v>
+        <v>297.1414885700001</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17942,28 +17997,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1151230219485849</v>
+        <v>0.1122914008917209</v>
       </c>
       <c r="J5" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K5" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02774676083709893</v>
+        <v>0.02654974635402785</v>
       </c>
       <c r="M5" t="n">
-        <v>3.789281458827617</v>
+        <v>3.78876186457473</v>
       </c>
       <c r="N5" t="n">
-        <v>24.29852237837322</v>
+        <v>24.28014585638973</v>
       </c>
       <c r="O5" t="n">
-        <v>4.929353139953885</v>
+        <v>4.92748879820033</v>
       </c>
       <c r="P5" t="n">
-        <v>298.6127926202687</v>
+        <v>298.6431806516047</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18020,28 +18075,28 @@
         <v>0.0916</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09287423340581737</v>
+        <v>0.08858465688128075</v>
       </c>
       <c r="J6" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K6" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01933651193083696</v>
+        <v>0.01763826635315946</v>
       </c>
       <c r="M6" t="n">
-        <v>3.823818594596659</v>
+        <v>3.831030468726402</v>
       </c>
       <c r="N6" t="n">
-        <v>22.8886800737882</v>
+        <v>22.95289448610654</v>
       </c>
       <c r="O6" t="n">
-        <v>4.784211541496489</v>
+        <v>4.79091791686171</v>
       </c>
       <c r="P6" t="n">
-        <v>305.1835684906944</v>
+        <v>305.2296028234064</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18098,28 +18153,28 @@
         <v>0.1115</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09038083149206187</v>
+        <v>0.08846297920660558</v>
       </c>
       <c r="J7" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K7" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02217107225480996</v>
+        <v>0.02137453085799335</v>
       </c>
       <c r="M7" t="n">
-        <v>3.413418958100146</v>
+        <v>3.411425857349557</v>
       </c>
       <c r="N7" t="n">
-        <v>18.85025557754842</v>
+        <v>18.81689452667716</v>
       </c>
       <c r="O7" t="n">
-        <v>4.341688102287914</v>
+        <v>4.33784445625672</v>
       </c>
       <c r="P7" t="n">
-        <v>314.9063411984405</v>
+        <v>314.9269229620938</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18176,28 +18231,28 @@
         <v>0.0945</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05871398841508267</v>
+        <v>0.06061005603375658</v>
       </c>
       <c r="J8" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K8" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009275674622765018</v>
+        <v>0.00993292503118115</v>
       </c>
       <c r="M8" t="n">
-        <v>3.406624507763757</v>
+        <v>3.403998448148193</v>
       </c>
       <c r="N8" t="n">
-        <v>19.26543769804213</v>
+        <v>19.23010859464071</v>
       </c>
       <c r="O8" t="n">
-        <v>4.389241130086399</v>
+        <v>4.385214771780364</v>
       </c>
       <c r="P8" t="n">
-        <v>317.734026638037</v>
+        <v>317.7136786603047</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18254,28 +18309,28 @@
         <v>0.0588</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1516081105170998</v>
+        <v>0.1556722874734438</v>
       </c>
       <c r="J9" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K9" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04903867126502837</v>
+        <v>0.05164584580171427</v>
       </c>
       <c r="M9" t="n">
-        <v>3.482044312836493</v>
+        <v>3.494503534806446</v>
       </c>
       <c r="N9" t="n">
-        <v>23.32155084136559</v>
+        <v>23.37021329057869</v>
       </c>
       <c r="O9" t="n">
-        <v>4.829239157607086</v>
+        <v>4.834274846404442</v>
       </c>
       <c r="P9" t="n">
-        <v>323.1944274158562</v>
+        <v>323.1508119976119</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18332,28 +18387,28 @@
         <v>0.0578</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04443285990184843</v>
+        <v>0.04782430767454482</v>
       </c>
       <c r="J10" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K10" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L10" t="n">
-        <v>0.004289773421491838</v>
+        <v>0.004982841920141645</v>
       </c>
       <c r="M10" t="n">
-        <v>3.376110159467897</v>
+        <v>3.385625769531631</v>
       </c>
       <c r="N10" t="n">
-        <v>23.97703859222204</v>
+        <v>23.98588510186009</v>
       </c>
       <c r="O10" t="n">
-        <v>4.896635435911279</v>
+        <v>4.897538677934059</v>
       </c>
       <c r="P10" t="n">
-        <v>337.5646281628001</v>
+        <v>337.5282322541946</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18410,28 +18465,28 @@
         <v>0.0639</v>
       </c>
       <c r="I11" t="n">
-        <v>0.002271656539345206</v>
+        <v>0.004030560483472188</v>
       </c>
       <c r="J11" t="n">
+        <v>309</v>
+      </c>
+      <c r="K11" t="n">
         <v>308</v>
       </c>
-      <c r="K11" t="n">
-        <v>307</v>
-      </c>
       <c r="L11" t="n">
-        <v>1.633737298789573e-05</v>
+        <v>5.171733169917481e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>2.982029123125597</v>
+        <v>2.980351992468839</v>
       </c>
       <c r="N11" t="n">
-        <v>16.56492471225877</v>
+        <v>16.53437064787978</v>
       </c>
       <c r="O11" t="n">
-        <v>4.070003035902894</v>
+        <v>4.066247735674719</v>
       </c>
       <c r="P11" t="n">
-        <v>340.111817950189</v>
+        <v>340.0929739527952</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -18488,28 +18543,28 @@
         <v>0.0709</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08806487808954415</v>
+        <v>0.08431391663240043</v>
       </c>
       <c r="J12" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K12" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01567095753665215</v>
+        <v>0.01442312123641187</v>
       </c>
       <c r="M12" t="n">
-        <v>3.957417835999941</v>
+        <v>3.961454078952032</v>
       </c>
       <c r="N12" t="n">
-        <v>25.48816886995258</v>
+        <v>25.51142311986131</v>
       </c>
       <c r="O12" t="n">
-        <v>5.048580876835844</v>
+        <v>5.050883399947113</v>
       </c>
       <c r="P12" t="n">
-        <v>329.4235510285406</v>
+        <v>329.4638051204586</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -18547,7 +18602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M309"/>
+  <dimension ref="A1:M310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39249,6 +39304,73 @@
         </is>
       </c>
     </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>-35.55972978523634,174.48615671272543</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>-35.56010049506934,174.48693891936364</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>-35.56044137255204,174.48773676264457</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>-35.56072697774938,174.48856357604427</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>-35.560990536271504,174.48940445928912</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>-35.5611780948098,174.49031313946705</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>-35.561337112291646,174.49122071993287</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>-35.5614599613795,174.492113602543</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>-35.561593592442094,174.49302749080843</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>-35.56165575989269,174.4939469277363</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>-35.5618226416776,174.49484831950997</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0090/nzd0090.xlsx
+++ b/data/nzd0090/nzd0090.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M310"/>
+  <dimension ref="A1:M311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14398,6 +14398,51 @@
       <c r="M310" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>312.25</v>
+      </c>
+      <c r="C311" t="n">
+        <v>302.92</v>
+      </c>
+      <c r="D311" t="n">
+        <v>298.14</v>
+      </c>
+      <c r="E311" t="n">
+        <v>298.32</v>
+      </c>
+      <c r="F311" t="n">
+        <v>303.73</v>
+      </c>
+      <c r="G311" t="n">
+        <v>317.07</v>
+      </c>
+      <c r="H311" t="n">
+        <v>325.64</v>
+      </c>
+      <c r="I311" t="n">
+        <v>336.36</v>
+      </c>
+      <c r="J311" t="n">
+        <v>346.48</v>
+      </c>
+      <c r="K311" t="n">
+        <v>344.13</v>
+      </c>
+      <c r="L311" t="n">
+        <v>328.82</v>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -14412,7 +14457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B318"/>
+  <dimension ref="A1:B319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17595,6 +17640,16 @@
       </c>
       <c r="B318" t="n">
         <v>0.72</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>0.41</v>
       </c>
     </row>
   </sheetData>
@@ -17763,28 +17818,28 @@
         <v>0.0819</v>
       </c>
       <c r="I2" t="n">
-        <v>0.146919054532744</v>
+        <v>0.1468963700106178</v>
       </c>
       <c r="J2" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K2" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0602173102808099</v>
+        <v>0.06059783303139399</v>
       </c>
       <c r="M2" t="n">
-        <v>3.033996425064482</v>
+        <v>3.024328556542304</v>
       </c>
       <c r="N2" t="n">
-        <v>17.69160536319646</v>
+        <v>17.63453952290508</v>
       </c>
       <c r="O2" t="n">
-        <v>4.206139009019608</v>
+        <v>4.199349892888789</v>
       </c>
       <c r="P2" t="n">
-        <v>308.407127235697</v>
+        <v>308.4073718289928</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17841,28 +17896,28 @@
         <v>0.1027</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1414740191421134</v>
+        <v>0.1414019800344478</v>
       </c>
       <c r="J3" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K3" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05626011236616957</v>
+        <v>0.05657912726675385</v>
       </c>
       <c r="M3" t="n">
-        <v>3.113906703563941</v>
+        <v>3.104226398609041</v>
       </c>
       <c r="N3" t="n">
-        <v>17.63234213823831</v>
+        <v>17.57550248725662</v>
       </c>
       <c r="O3" t="n">
-        <v>4.19908825082759</v>
+        <v>4.192314693252001</v>
       </c>
       <c r="P3" t="n">
-        <v>299.2924307010119</v>
+        <v>299.2932074545482</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17919,28 +17974,28 @@
         <v>0.1427</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08803221354728159</v>
+        <v>0.08716979465934033</v>
       </c>
       <c r="J4" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K4" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01633585451113029</v>
+        <v>0.01612977985995168</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6389414353756</v>
+        <v>3.630980446720551</v>
       </c>
       <c r="N4" t="n">
-        <v>24.50716836733871</v>
+        <v>24.43368403808314</v>
       </c>
       <c r="O4" t="n">
-        <v>4.950471529797815</v>
+        <v>4.9430440052748</v>
       </c>
       <c r="P4" t="n">
-        <v>297.1414885700001</v>
+        <v>297.1507875041855</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17997,28 +18052,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1122914008917209</v>
+        <v>0.1101475889040982</v>
       </c>
       <c r="J5" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K5" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02654974635402785</v>
+        <v>0.02571105587263123</v>
       </c>
       <c r="M5" t="n">
-        <v>3.78876186457473</v>
+        <v>3.785344510151858</v>
       </c>
       <c r="N5" t="n">
-        <v>24.28014585638973</v>
+        <v>24.23624781944184</v>
       </c>
       <c r="O5" t="n">
-        <v>4.92748879820033</v>
+        <v>4.923032380499019</v>
       </c>
       <c r="P5" t="n">
-        <v>298.6431806516047</v>
+        <v>298.6662960620597</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18075,28 +18130,28 @@
         <v>0.0916</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08858465688128075</v>
+        <v>0.08607692074839436</v>
       </c>
       <c r="J6" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K6" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01763826635315946</v>
+        <v>0.01675161692706573</v>
       </c>
       <c r="M6" t="n">
-        <v>3.831030468726402</v>
+        <v>3.830132565887435</v>
       </c>
       <c r="N6" t="n">
-        <v>22.95289448610654</v>
+        <v>22.92595760952605</v>
       </c>
       <c r="O6" t="n">
-        <v>4.79091791686171</v>
+        <v>4.788105847778018</v>
       </c>
       <c r="P6" t="n">
-        <v>305.2296028234064</v>
+        <v>305.2566422048255</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18153,28 +18208,28 @@
         <v>0.1115</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08846297920660558</v>
+        <v>0.08833563227138207</v>
       </c>
       <c r="J7" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K7" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02137453085799335</v>
+        <v>0.02146100057974376</v>
       </c>
       <c r="M7" t="n">
-        <v>3.411425857349557</v>
+        <v>3.401022960993972</v>
       </c>
       <c r="N7" t="n">
-        <v>18.81689452667716</v>
+        <v>18.75631633934751</v>
       </c>
       <c r="O7" t="n">
-        <v>4.33784445625672</v>
+        <v>4.330856305552922</v>
       </c>
       <c r="P7" t="n">
-        <v>314.9269229620938</v>
+        <v>314.9282960660297</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18231,28 +18286,28 @@
         <v>0.0945</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06061005603375658</v>
+        <v>0.06474070111568193</v>
       </c>
       <c r="J8" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K8" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00993292503118115</v>
+        <v>0.01132121421029608</v>
       </c>
       <c r="M8" t="n">
-        <v>3.403998448148193</v>
+        <v>3.411059476913405</v>
       </c>
       <c r="N8" t="n">
-        <v>19.23010859464071</v>
+        <v>19.29587764756155</v>
       </c>
       <c r="O8" t="n">
-        <v>4.385214771780364</v>
+        <v>4.392707325506851</v>
       </c>
       <c r="P8" t="n">
-        <v>317.7136786603047</v>
+        <v>317.6691404465697</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18309,28 +18364,28 @@
         <v>0.0588</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1556722874734438</v>
+        <v>0.1616150902561078</v>
       </c>
       <c r="J9" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K9" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05164584580171427</v>
+        <v>0.05521785442776284</v>
       </c>
       <c r="M9" t="n">
-        <v>3.494503534806446</v>
+        <v>3.518008006936482</v>
       </c>
       <c r="N9" t="n">
-        <v>23.37021329057869</v>
+        <v>23.5593606479496</v>
       </c>
       <c r="O9" t="n">
-        <v>4.834274846404442</v>
+        <v>4.853798579252089</v>
       </c>
       <c r="P9" t="n">
-        <v>323.1508119976119</v>
+        <v>323.0867343982856</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18387,28 +18442,28 @@
         <v>0.0578</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04782430767454482</v>
+        <v>0.05284478466764531</v>
       </c>
       <c r="J10" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K10" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L10" t="n">
-        <v>0.004982841920141645</v>
+        <v>0.006072089779573853</v>
       </c>
       <c r="M10" t="n">
-        <v>3.385625769531631</v>
+        <v>3.405074414138243</v>
       </c>
       <c r="N10" t="n">
-        <v>23.98588510186009</v>
+        <v>24.09730637113402</v>
       </c>
       <c r="O10" t="n">
-        <v>4.897538677934059</v>
+        <v>4.908900729403072</v>
       </c>
       <c r="P10" t="n">
-        <v>337.5282322541946</v>
+        <v>337.4740995284495</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18465,28 +18520,28 @@
         <v>0.0639</v>
       </c>
       <c r="I11" t="n">
-        <v>0.004030560483472188</v>
+        <v>0.006599945566114599</v>
       </c>
       <c r="J11" t="n">
+        <v>310</v>
+      </c>
+      <c r="K11" t="n">
         <v>309</v>
       </c>
-      <c r="K11" t="n">
-        <v>308</v>
-      </c>
       <c r="L11" t="n">
-        <v>5.171733169917481e-05</v>
+        <v>0.0001392206522323747</v>
       </c>
       <c r="M11" t="n">
-        <v>2.980351992468839</v>
+        <v>2.982239995135333</v>
       </c>
       <c r="N11" t="n">
-        <v>16.53437064787978</v>
+        <v>16.5302661940236</v>
       </c>
       <c r="O11" t="n">
-        <v>4.066247735674719</v>
+        <v>4.065743006391771</v>
       </c>
       <c r="P11" t="n">
-        <v>340.0929739527952</v>
+        <v>340.0653165735237</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -18543,28 +18598,28 @@
         <v>0.0709</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08431391663240043</v>
+        <v>0.0824385203289896</v>
       </c>
       <c r="J12" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K12" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01442312123641187</v>
+        <v>0.01387896146356649</v>
       </c>
       <c r="M12" t="n">
-        <v>3.961454078952032</v>
+        <v>3.957101438587197</v>
       </c>
       <c r="N12" t="n">
-        <v>25.51142311986131</v>
+        <v>25.45547251785002</v>
       </c>
       <c r="O12" t="n">
-        <v>5.050883399947113</v>
+        <v>5.045341665125368</v>
       </c>
       <c r="P12" t="n">
-        <v>329.4638051204586</v>
+        <v>329.4840263691358</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -18602,7 +18657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M310"/>
+  <dimension ref="A1:M311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39371,6 +39426,73 @@
         </is>
       </c>
     </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>-35.55972141585364,174.4861610995476</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>-35.560092622862705,174.4869430455512</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>-35.56042612530074,174.4877447543511</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>-35.560718525451215,174.488568006187</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>-35.560968295831536,174.48941600614867</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>-35.5611549503117,174.49032337666583</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>-35.561307276906675,174.4912318486729</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>-35.56143443742677,174.4921231229073</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>-35.561570966491296,174.49303245824467</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>-35.5616443181122,174.49394740764413</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>-35.561797131785475,174.4948486372402</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0090/nzd0090.xlsx
+++ b/data/nzd0090/nzd0090.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M311"/>
+  <dimension ref="A1:M312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14443,6 +14443,51 @@
       <c r="M311" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>311.33</v>
+      </c>
+      <c r="C312" t="n">
+        <v>302.42</v>
+      </c>
+      <c r="D312" t="n">
+        <v>297.58</v>
+      </c>
+      <c r="E312" t="n">
+        <v>296.82</v>
+      </c>
+      <c r="F312" t="n">
+        <v>303.1</v>
+      </c>
+      <c r="G312" t="n">
+        <v>316.38</v>
+      </c>
+      <c r="H312" t="n">
+        <v>324.15</v>
+      </c>
+      <c r="I312" t="n">
+        <v>334.74</v>
+      </c>
+      <c r="J312" t="n">
+        <v>343.73</v>
+      </c>
+      <c r="K312" t="n">
+        <v>344.87</v>
+      </c>
+      <c r="L312" t="n">
+        <v>332.31</v>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -14457,7 +14502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B319"/>
+  <dimension ref="A1:B320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17650,6 +17695,16 @@
       </c>
       <c r="B319" t="n">
         <v>0.41</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>-0.61</v>
       </c>
     </row>
   </sheetData>
@@ -17818,28 +17873,28 @@
         <v>0.0819</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1468963700106178</v>
+        <v>0.1462560375905397</v>
       </c>
       <c r="J2" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K2" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06059783303139399</v>
+        <v>0.06049598456126792</v>
       </c>
       <c r="M2" t="n">
-        <v>3.024328556542304</v>
+        <v>3.017913173581892</v>
       </c>
       <c r="N2" t="n">
-        <v>17.63453952290508</v>
+        <v>17.58087393164293</v>
       </c>
       <c r="O2" t="n">
-        <v>4.199349892888789</v>
+        <v>4.192955274224009</v>
       </c>
       <c r="P2" t="n">
-        <v>308.4073718289928</v>
+        <v>308.414320958441</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17896,28 +17951,28 @@
         <v>0.1027</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1414019800344478</v>
+        <v>0.1409888884826024</v>
       </c>
       <c r="J3" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K3" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05657912726675385</v>
+        <v>0.05664299710340548</v>
       </c>
       <c r="M3" t="n">
-        <v>3.104226398609041</v>
+        <v>3.096301553450618</v>
       </c>
       <c r="N3" t="n">
-        <v>17.57550248725662</v>
+        <v>17.52025360247854</v>
       </c>
       <c r="O3" t="n">
-        <v>4.192314693252001</v>
+        <v>4.185720201169512</v>
       </c>
       <c r="P3" t="n">
-        <v>299.2932074545482</v>
+        <v>299.2976904802044</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17974,28 +18029,28 @@
         <v>0.1427</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08716979465934033</v>
+        <v>0.08593545622656799</v>
       </c>
       <c r="J4" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K4" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01612977985995168</v>
+        <v>0.01578641231308642</v>
       </c>
       <c r="M4" t="n">
-        <v>3.630980446720551</v>
+        <v>3.624631734957727</v>
       </c>
       <c r="N4" t="n">
-        <v>24.43368403808314</v>
+        <v>24.36640455906726</v>
       </c>
       <c r="O4" t="n">
-        <v>4.9430440052748</v>
+        <v>4.936233843636995</v>
       </c>
       <c r="P4" t="n">
-        <v>297.1507875041855</v>
+        <v>297.164183011399</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18052,28 +18107,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1101475889040982</v>
+        <v>0.1070219166803767</v>
       </c>
       <c r="J5" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K5" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02571105587263123</v>
+        <v>0.02440561899254967</v>
       </c>
       <c r="M5" t="n">
-        <v>3.785344510151858</v>
+        <v>3.785906311172804</v>
       </c>
       <c r="N5" t="n">
-        <v>24.23624781944184</v>
+        <v>24.23068402497541</v>
       </c>
       <c r="O5" t="n">
-        <v>4.923032380499019</v>
+        <v>4.922467270076604</v>
       </c>
       <c r="P5" t="n">
-        <v>298.6662960620597</v>
+        <v>298.700217038437</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18130,28 +18185,28 @@
         <v>0.0916</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08607692074839436</v>
+        <v>0.08316447495097276</v>
       </c>
       <c r="J6" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K6" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01675161692706573</v>
+        <v>0.01572218714555706</v>
       </c>
       <c r="M6" t="n">
-        <v>3.830132565887435</v>
+        <v>3.831252916078397</v>
       </c>
       <c r="N6" t="n">
-        <v>22.92595760952605</v>
+        <v>22.91507040337979</v>
       </c>
       <c r="O6" t="n">
-        <v>4.788105847778018</v>
+        <v>4.786968811615529</v>
       </c>
       <c r="P6" t="n">
-        <v>305.2566422048255</v>
+        <v>305.2882491674318</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18208,28 +18263,28 @@
         <v>0.1115</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08833563227138207</v>
+        <v>0.08775121601481452</v>
       </c>
       <c r="J7" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K7" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02146100057974376</v>
+        <v>0.02132927194284184</v>
       </c>
       <c r="M7" t="n">
-        <v>3.401022960993972</v>
+        <v>3.392801228036358</v>
       </c>
       <c r="N7" t="n">
-        <v>18.75631633934751</v>
+        <v>18.69853648516447</v>
       </c>
       <c r="O7" t="n">
-        <v>4.330856305552922</v>
+        <v>4.324180440865584</v>
       </c>
       <c r="P7" t="n">
-        <v>314.9282960660297</v>
+        <v>314.9346383721369</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18286,28 +18341,28 @@
         <v>0.0945</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06474070111568193</v>
+        <v>0.06786327763124128</v>
       </c>
       <c r="J8" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K8" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01132121421029608</v>
+        <v>0.0124671848339879</v>
       </c>
       <c r="M8" t="n">
-        <v>3.411059476913405</v>
+        <v>3.413484471649989</v>
       </c>
       <c r="N8" t="n">
-        <v>19.29587764756155</v>
+        <v>19.30605601366051</v>
       </c>
       <c r="O8" t="n">
-        <v>4.392707325506851</v>
+        <v>4.393865725492815</v>
       </c>
       <c r="P8" t="n">
-        <v>317.6691404465697</v>
+        <v>317.6352530659874</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18364,28 +18419,28 @@
         <v>0.0588</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1616150902561078</v>
+        <v>0.1664401897706263</v>
       </c>
       <c r="J9" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K9" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05521785442776284</v>
+        <v>0.05835803017217622</v>
       </c>
       <c r="M9" t="n">
-        <v>3.518008006936482</v>
+        <v>3.534998087580211</v>
       </c>
       <c r="N9" t="n">
-        <v>23.5593606479496</v>
+        <v>23.65605653245039</v>
       </c>
       <c r="O9" t="n">
-        <v>4.853798579252089</v>
+        <v>4.863749225900775</v>
       </c>
       <c r="P9" t="n">
-        <v>323.0867343982856</v>
+        <v>323.0343705946186</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18442,28 +18497,28 @@
         <v>0.0578</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05284478466764531</v>
+        <v>0.05602908351631913</v>
       </c>
       <c r="J10" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K10" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006072089779573853</v>
+        <v>0.006847907757404292</v>
       </c>
       <c r="M10" t="n">
-        <v>3.405074414138243</v>
+        <v>3.413156324209423</v>
       </c>
       <c r="N10" t="n">
-        <v>24.09730637113402</v>
+        <v>24.09492946608505</v>
       </c>
       <c r="O10" t="n">
-        <v>4.908900729403072</v>
+        <v>4.908658621872686</v>
       </c>
       <c r="P10" t="n">
-        <v>337.4740995284495</v>
+        <v>337.4395423137791</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18520,28 +18575,28 @@
         <v>0.0639</v>
       </c>
       <c r="I11" t="n">
-        <v>0.006599945566114599</v>
+        <v>0.009638290831609112</v>
       </c>
       <c r="J11" t="n">
+        <v>311</v>
+      </c>
+      <c r="K11" t="n">
         <v>310</v>
       </c>
-      <c r="K11" t="n">
-        <v>309</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.0001392206522323747</v>
+        <v>0.0002977547400709879</v>
       </c>
       <c r="M11" t="n">
-        <v>2.982239995135333</v>
+        <v>2.986102375323694</v>
       </c>
       <c r="N11" t="n">
-        <v>16.5302661940236</v>
+        <v>16.54526658426844</v>
       </c>
       <c r="O11" t="n">
-        <v>4.065743006391771</v>
+        <v>4.06758731735023</v>
       </c>
       <c r="P11" t="n">
-        <v>340.0653165735237</v>
+        <v>340.0323985460068</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -18598,28 +18653,28 @@
         <v>0.0709</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0824385203289896</v>
+        <v>0.08285422361149661</v>
       </c>
       <c r="J12" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K12" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01387896146356649</v>
+        <v>0.01411535459854019</v>
       </c>
       <c r="M12" t="n">
-        <v>3.957101438587197</v>
+        <v>3.946580321230177</v>
       </c>
       <c r="N12" t="n">
-        <v>25.45547251785002</v>
+        <v>25.37490214222369</v>
       </c>
       <c r="O12" t="n">
-        <v>5.045341665125368</v>
+        <v>5.03735070669332</v>
       </c>
       <c r="P12" t="n">
-        <v>329.4840263691358</v>
+        <v>329.4795149999913</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -18657,7 +18712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M311"/>
+  <dimension ref="A1:M312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39493,6 +39548,73 @@
         </is>
       </c>
     </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>-35.55972903944977,174.4861571036304</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>-35.56009676612937,174.48694087387364</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>-35.56043076576857,174.4877423220929</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>-35.560730955301395,174.4885614912709</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>-35.56097352399476,174.48941329177552</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>-35.56116080002009,174.4903207892425</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>-35.561320125092806,174.49122705623958</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>-35.5614484066172,174.49211791243835</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>-35.56159536702646,174.4930271012055</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>-35.56163765124798,174.4939476872754</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>-35.56176567258975,174.49484902907022</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0090/nzd0090.xlsx
+++ b/data/nzd0090/nzd0090.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M312"/>
+  <dimension ref="A1:M314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14486,6 +14486,96 @@
         <v>332.31</v>
       </c>
       <c r="M312" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>310.18</v>
+      </c>
+      <c r="C313" t="n">
+        <v>302</v>
+      </c>
+      <c r="D313" t="n">
+        <v>296.88</v>
+      </c>
+      <c r="E313" t="n">
+        <v>296.63</v>
+      </c>
+      <c r="F313" t="n">
+        <v>303.52</v>
+      </c>
+      <c r="G313" t="n">
+        <v>315.44</v>
+      </c>
+      <c r="H313" t="n">
+        <v>322.6</v>
+      </c>
+      <c r="I313" t="n">
+        <v>329.95</v>
+      </c>
+      <c r="J313" t="n">
+        <v>340.39</v>
+      </c>
+      <c r="K313" t="n">
+        <v>342.78</v>
+      </c>
+      <c r="L313" t="n">
+        <v>330.58</v>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>309.75</v>
+      </c>
+      <c r="C314" t="n">
+        <v>301.55</v>
+      </c>
+      <c r="D314" t="n">
+        <v>297.39</v>
+      </c>
+      <c r="E314" t="n">
+        <v>296.6</v>
+      </c>
+      <c r="F314" t="n">
+        <v>304.24</v>
+      </c>
+      <c r="G314" t="n">
+        <v>313.5</v>
+      </c>
+      <c r="H314" t="n">
+        <v>318.96</v>
+      </c>
+      <c r="I314" t="n">
+        <v>327.54</v>
+      </c>
+      <c r="J314" t="n">
+        <v>337.71</v>
+      </c>
+      <c r="K314" t="n">
+        <v>341.52</v>
+      </c>
+      <c r="L314" t="n">
+        <v>328.84</v>
+      </c>
+      <c r="M314" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14502,7 +14592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B320"/>
+  <dimension ref="A1:B322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17705,6 +17795,26 @@
       </c>
       <c r="B320" t="n">
         <v>-0.61</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>-0.1</v>
       </c>
     </row>
   </sheetData>
@@ -17873,28 +17983,28 @@
         <v>0.0819</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1462560375905397</v>
+        <v>0.1432254890667194</v>
       </c>
       <c r="J2" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K2" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06049598456126792</v>
+        <v>0.0588294065031193</v>
       </c>
       <c r="M2" t="n">
-        <v>3.017913173581892</v>
+        <v>3.014386081271756</v>
       </c>
       <c r="N2" t="n">
-        <v>17.58087393164293</v>
+        <v>17.50320189766315</v>
       </c>
       <c r="O2" t="n">
-        <v>4.192955274224009</v>
+        <v>4.183682815135865</v>
       </c>
       <c r="P2" t="n">
-        <v>308.414320958441</v>
+        <v>308.447315926657</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17951,28 +18061,28 @@
         <v>0.1027</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1409888884826024</v>
+        <v>0.1393427031727249</v>
       </c>
       <c r="J3" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K3" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05664299710340548</v>
+        <v>0.05611428233703497</v>
       </c>
       <c r="M3" t="n">
-        <v>3.096301553450618</v>
+        <v>3.084605572616107</v>
       </c>
       <c r="N3" t="n">
-        <v>17.52025360247854</v>
+        <v>17.41876887539224</v>
       </c>
       <c r="O3" t="n">
-        <v>4.185720201169512</v>
+        <v>4.17357986330587</v>
       </c>
       <c r="P3" t="n">
-        <v>299.2976904802044</v>
+        <v>299.315613954297</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18029,28 +18139,28 @@
         <v>0.1427</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08593545622656799</v>
+        <v>0.08293662631792266</v>
       </c>
       <c r="J4" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K4" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01578641231308642</v>
+        <v>0.01490579752825549</v>
       </c>
       <c r="M4" t="n">
-        <v>3.624631734957727</v>
+        <v>3.614657240589195</v>
       </c>
       <c r="N4" t="n">
-        <v>24.36640455906726</v>
+        <v>24.24478114544889</v>
       </c>
       <c r="O4" t="n">
-        <v>4.936233843636995</v>
+        <v>4.92389897798979</v>
       </c>
       <c r="P4" t="n">
-        <v>297.164183011399</v>
+        <v>297.1968295955442</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18107,28 +18217,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1070219166803767</v>
+        <v>0.1006393735238339</v>
       </c>
       <c r="J5" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K5" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02440561899254967</v>
+        <v>0.02180919273603454</v>
       </c>
       <c r="M5" t="n">
-        <v>3.785906311172804</v>
+        <v>3.787642890154955</v>
       </c>
       <c r="N5" t="n">
-        <v>24.23068402497541</v>
+        <v>24.22829361871242</v>
       </c>
       <c r="O5" t="n">
-        <v>4.922467270076604</v>
+        <v>4.922224458383874</v>
       </c>
       <c r="P5" t="n">
-        <v>298.700217038437</v>
+        <v>298.7697038047717</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18185,28 +18295,28 @@
         <v>0.0916</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08316447495097276</v>
+        <v>0.0784751748335762</v>
       </c>
       <c r="J6" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K6" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01572218714555706</v>
+        <v>0.01416935038012324</v>
       </c>
       <c r="M6" t="n">
-        <v>3.831252916078397</v>
+        <v>3.828214855675307</v>
       </c>
       <c r="N6" t="n">
-        <v>22.91507040337979</v>
+        <v>22.85177570757169</v>
       </c>
       <c r="O6" t="n">
-        <v>4.786968811615529</v>
+        <v>4.780353094445188</v>
       </c>
       <c r="P6" t="n">
-        <v>305.2882491674318</v>
+        <v>305.339299202406</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18263,28 +18373,28 @@
         <v>0.1115</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08775121601481452</v>
+        <v>0.08413065618920004</v>
       </c>
       <c r="J7" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K7" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02132927194284184</v>
+        <v>0.01985608998010269</v>
       </c>
       <c r="M7" t="n">
-        <v>3.392801228036358</v>
+        <v>3.38802706690187</v>
       </c>
       <c r="N7" t="n">
-        <v>18.69853648516447</v>
+        <v>18.63406724657868</v>
       </c>
       <c r="O7" t="n">
-        <v>4.324180440865584</v>
+        <v>4.316719500567379</v>
       </c>
       <c r="P7" t="n">
-        <v>314.9346383721369</v>
+        <v>314.974061649373</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18341,28 +18451,28 @@
         <v>0.0945</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06786327763124128</v>
+        <v>0.06958780477468186</v>
       </c>
       <c r="J8" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K8" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0124671848339879</v>
+        <v>0.01326264705661273</v>
       </c>
       <c r="M8" t="n">
-        <v>3.413484471649989</v>
+        <v>3.402287853796962</v>
       </c>
       <c r="N8" t="n">
-        <v>19.30605601366051</v>
+        <v>19.2150102915422</v>
       </c>
       <c r="O8" t="n">
-        <v>4.393865725492815</v>
+        <v>4.383492932758327</v>
       </c>
       <c r="P8" t="n">
-        <v>317.6352530659874</v>
+        <v>317.6164899503576</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18419,28 +18529,28 @@
         <v>0.0588</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1664401897706263</v>
+        <v>0.1680898379669567</v>
       </c>
       <c r="J9" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K9" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05835803017217622</v>
+        <v>0.06020084289825811</v>
       </c>
       <c r="M9" t="n">
-        <v>3.534998087580211</v>
+        <v>3.522181032621139</v>
       </c>
       <c r="N9" t="n">
-        <v>23.65605653245039</v>
+        <v>23.52439096007929</v>
       </c>
       <c r="O9" t="n">
-        <v>4.863749225900775</v>
+        <v>4.850194940420363</v>
       </c>
       <c r="P9" t="n">
-        <v>323.0343705946186</v>
+        <v>323.0164187058868</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18497,28 +18607,28 @@
         <v>0.0578</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05602908351631913</v>
+        <v>0.05617882394296705</v>
       </c>
       <c r="J10" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K10" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006847907757404292</v>
+        <v>0.006978384936268012</v>
       </c>
       <c r="M10" t="n">
-        <v>3.413156324209423</v>
+        <v>3.400083707326099</v>
       </c>
       <c r="N10" t="n">
-        <v>24.09492946608505</v>
+        <v>23.95256673750351</v>
       </c>
       <c r="O10" t="n">
-        <v>4.908658621872686</v>
+        <v>4.894135954129545</v>
       </c>
       <c r="P10" t="n">
-        <v>337.4395423137791</v>
+        <v>337.4379207919555</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18575,28 +18685,28 @@
         <v>0.0639</v>
       </c>
       <c r="I11" t="n">
-        <v>0.009638290831609112</v>
+        <v>0.01204691879910275</v>
       </c>
       <c r="J11" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K11" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0002977547400709879</v>
+        <v>0.0004710421256350905</v>
       </c>
       <c r="M11" t="n">
-        <v>2.986102375323694</v>
+        <v>2.977563137187426</v>
       </c>
       <c r="N11" t="n">
-        <v>16.54526658426844</v>
+        <v>16.46347462858923</v>
       </c>
       <c r="O11" t="n">
-        <v>4.06758731735023</v>
+        <v>4.057520749002921</v>
       </c>
       <c r="P11" t="n">
-        <v>340.0323985460068</v>
+        <v>340.006223726152</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -18653,28 +18763,28 @@
         <v>0.0709</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08285422361149661</v>
+        <v>0.08029715539481536</v>
       </c>
       <c r="J12" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K12" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01411535459854019</v>
+        <v>0.01344008227787263</v>
       </c>
       <c r="M12" t="n">
-        <v>3.946580321230177</v>
+        <v>3.932737246826329</v>
       </c>
       <c r="N12" t="n">
-        <v>25.37490214222369</v>
+        <v>25.24206334050105</v>
       </c>
       <c r="O12" t="n">
-        <v>5.03735070669332</v>
+        <v>5.024148021356561</v>
       </c>
       <c r="P12" t="n">
-        <v>329.4795149999913</v>
+        <v>329.5073594274765</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -18712,7 +18822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M312"/>
+  <dimension ref="A1:M314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39615,6 +39725,140 @@
         </is>
       </c>
     </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>-35.55973856894477,174.4861521087329</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>-35.56010024647334,174.48693904966433</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>-35.560436566353324,174.48773928176976</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>-35.56073252974907,174.48856066604807</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>-35.56097003855262,174.48941510135765</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>-35.56116876918795,174.49031726434634</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>-35.56133349065537,174.49122207082084</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>-35.56148971058024,174.49210250616514</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>-35.56162500258517,174.49302059483392</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>-35.56165648063477,174.49394689750588</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>-35.56178126697619,174.4948488348393</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>-35.559742132147214,174.48615024107528</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>-35.560103975413284,174.4869370951542</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>-35.56043234021301,174.48774149686238</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>-35.560732778346065,174.4885605357497</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>-35.56096406350889,174.4894182034981</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>-35.56118521619365,174.49030998955857</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>-35.56136487816928,174.49121036312152</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>-35.56151049190541,174.49209475477772</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>-35.561648782015254,174.49301537414934</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>-35.56166783232246,174.49394642137673</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>-35.561796951503545,174.49484863948564</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0090/nzd0090.xlsx
+++ b/data/nzd0090/nzd0090.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M314"/>
+  <dimension ref="A1:M315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14578,6 +14578,51 @@
       <c r="M314" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>308.97</v>
+      </c>
+      <c r="C315" t="n">
+        <v>301.3</v>
+      </c>
+      <c r="D315" t="n">
+        <v>296.64</v>
+      </c>
+      <c r="E315" t="n">
+        <v>297.46</v>
+      </c>
+      <c r="F315" t="n">
+        <v>303.88</v>
+      </c>
+      <c r="G315" t="n">
+        <v>313.67</v>
+      </c>
+      <c r="H315" t="n">
+        <v>317.35</v>
+      </c>
+      <c r="I315" t="n">
+        <v>325.32</v>
+      </c>
+      <c r="J315" t="n">
+        <v>334.19</v>
+      </c>
+      <c r="K315" t="n">
+        <v>340.84</v>
+      </c>
+      <c r="L315" t="n">
+        <v>328.84</v>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -14592,7 +14637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B322"/>
+  <dimension ref="A1:B323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17815,6 +17860,16 @@
       </c>
       <c r="B322" t="n">
         <v>-0.1</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -17983,28 +18038,28 @@
         <v>0.0819</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1432254890667194</v>
+        <v>0.1410983169608582</v>
       </c>
       <c r="J2" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K2" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0588294065031193</v>
+        <v>0.05746803395558797</v>
       </c>
       <c r="M2" t="n">
-        <v>3.014386081271756</v>
+        <v>3.015883210743791</v>
       </c>
       <c r="N2" t="n">
-        <v>17.50320189766315</v>
+        <v>17.48178177640092</v>
       </c>
       <c r="O2" t="n">
-        <v>4.183682815135865</v>
+        <v>4.181122071454135</v>
       </c>
       <c r="P2" t="n">
-        <v>308.447315926657</v>
+        <v>308.4705485283084</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18061,28 +18116,28 @@
         <v>0.1027</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1393427031727249</v>
+        <v>0.1382257309433595</v>
       </c>
       <c r="J3" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K3" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05611428233703497</v>
+        <v>0.05560755316534094</v>
       </c>
       <c r="M3" t="n">
-        <v>3.084605572616107</v>
+        <v>3.08021760678041</v>
       </c>
       <c r="N3" t="n">
-        <v>17.41876887539224</v>
+        <v>17.37275874994229</v>
       </c>
       <c r="O3" t="n">
-        <v>4.17357986330587</v>
+        <v>4.168064148971593</v>
       </c>
       <c r="P3" t="n">
-        <v>299.315613954297</v>
+        <v>299.3278133296033</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18139,28 +18194,28 @@
         <v>0.1427</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08293662631792266</v>
+        <v>0.08114908267141102</v>
       </c>
       <c r="J4" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K4" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01490579752825549</v>
+        <v>0.0143644035683359</v>
       </c>
       <c r="M4" t="n">
-        <v>3.614657240589195</v>
+        <v>3.611141956359163</v>
       </c>
       <c r="N4" t="n">
-        <v>24.24478114544889</v>
+        <v>24.19180596111264</v>
       </c>
       <c r="O4" t="n">
-        <v>4.92389897798979</v>
+        <v>4.918516642353937</v>
       </c>
       <c r="P4" t="n">
-        <v>297.1968295955442</v>
+        <v>297.2163528345711</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18217,28 +18272,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1006393735238339</v>
+        <v>0.09806393408261989</v>
       </c>
       <c r="J5" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K5" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02180919273603454</v>
+        <v>0.02083086488590524</v>
       </c>
       <c r="M5" t="n">
-        <v>3.787642890154955</v>
+        <v>3.786036061551657</v>
       </c>
       <c r="N5" t="n">
-        <v>24.22829361871242</v>
+        <v>24.20144608702167</v>
       </c>
       <c r="O5" t="n">
-        <v>4.922224458383874</v>
+        <v>4.919496527798517</v>
       </c>
       <c r="P5" t="n">
-        <v>298.7697038047717</v>
+        <v>298.7978323038481</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18295,28 +18350,28 @@
         <v>0.0916</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0784751748335762</v>
+        <v>0.07618693699402361</v>
       </c>
       <c r="J6" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K6" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01416935038012324</v>
+        <v>0.01343591956713619</v>
       </c>
       <c r="M6" t="n">
-        <v>3.828214855675307</v>
+        <v>3.826388734250254</v>
       </c>
       <c r="N6" t="n">
-        <v>22.85177570757169</v>
+        <v>22.81871637949495</v>
       </c>
       <c r="O6" t="n">
-        <v>4.780353094445188</v>
+        <v>4.776894009656792</v>
       </c>
       <c r="P6" t="n">
-        <v>305.339299202406</v>
+        <v>305.3642909358269</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18373,28 +18428,28 @@
         <v>0.1115</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08413065618920004</v>
+        <v>0.08183977885549482</v>
       </c>
       <c r="J7" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K7" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01985608998010269</v>
+        <v>0.01890002254868806</v>
       </c>
       <c r="M7" t="n">
-        <v>3.38802706690187</v>
+        <v>3.388401430562493</v>
       </c>
       <c r="N7" t="n">
-        <v>18.63406724657868</v>
+        <v>18.61453179149197</v>
       </c>
       <c r="O7" t="n">
-        <v>4.316719500567379</v>
+        <v>4.31445614087013</v>
       </c>
       <c r="P7" t="n">
-        <v>314.974061649373</v>
+        <v>314.9990822108873</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18451,28 +18506,28 @@
         <v>0.0945</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06958780477468186</v>
+        <v>0.06822041358996381</v>
       </c>
       <c r="J8" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K8" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01326264705661273</v>
+        <v>0.0128326102384928</v>
       </c>
       <c r="M8" t="n">
-        <v>3.402287853796962</v>
+        <v>3.398934602303586</v>
       </c>
       <c r="N8" t="n">
-        <v>19.2150102915422</v>
+        <v>19.16799872548869</v>
       </c>
       <c r="O8" t="n">
-        <v>4.383492932758327</v>
+        <v>4.378127308049492</v>
       </c>
       <c r="P8" t="n">
-        <v>317.6164899503576</v>
+        <v>317.6314243576905</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18529,28 +18584,28 @@
         <v>0.0588</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1680898379669567</v>
+        <v>0.1666827665861998</v>
       </c>
       <c r="J9" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K9" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06020084289825811</v>
+        <v>0.05961405756574689</v>
       </c>
       <c r="M9" t="n">
-        <v>3.522181032621139</v>
+        <v>3.516464349772363</v>
       </c>
       <c r="N9" t="n">
-        <v>23.52439096007929</v>
+        <v>23.46449032986467</v>
       </c>
       <c r="O9" t="n">
-        <v>4.850194940420363</v>
+        <v>4.844015929976353</v>
       </c>
       <c r="P9" t="n">
-        <v>323.0164187058868</v>
+        <v>323.03178649338</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18607,28 +18662,28 @@
         <v>0.0578</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05617882394296705</v>
+        <v>0.05311700771467393</v>
       </c>
       <c r="J10" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K10" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006978384936268012</v>
+        <v>0.006268308247480259</v>
       </c>
       <c r="M10" t="n">
-        <v>3.400083707326099</v>
+        <v>3.401008973950082</v>
       </c>
       <c r="N10" t="n">
-        <v>23.95256673750351</v>
+        <v>23.94739500136792</v>
       </c>
       <c r="O10" t="n">
-        <v>4.894135954129545</v>
+        <v>4.893607565116754</v>
       </c>
       <c r="P10" t="n">
-        <v>337.4379207919555</v>
+        <v>337.4713614132225</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18685,28 +18740,28 @@
         <v>0.0639</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01204691879910275</v>
+        <v>0.01237984260141112</v>
       </c>
       <c r="J11" t="n">
+        <v>314</v>
+      </c>
+      <c r="K11" t="n">
         <v>313</v>
       </c>
-      <c r="K11" t="n">
-        <v>312</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.0004710421256350905</v>
+        <v>0.0005009179061092883</v>
       </c>
       <c r="M11" t="n">
-        <v>2.977563137187426</v>
+        <v>2.969499763026572</v>
       </c>
       <c r="N11" t="n">
-        <v>16.46347462858923</v>
+        <v>16.41171589499996</v>
       </c>
       <c r="O11" t="n">
-        <v>4.057520749002921</v>
+        <v>4.051137605043793</v>
       </c>
       <c r="P11" t="n">
-        <v>340.006223726152</v>
+        <v>340.0025936406203</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -18763,28 +18818,28 @@
         <v>0.0709</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08029715539481536</v>
+        <v>0.07848593747329485</v>
       </c>
       <c r="J12" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K12" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01344008227787263</v>
+        <v>0.01292519838439943</v>
       </c>
       <c r="M12" t="n">
-        <v>3.932737246826329</v>
+        <v>3.928234918377953</v>
       </c>
       <c r="N12" t="n">
-        <v>25.24206334050105</v>
+        <v>25.18655835360472</v>
       </c>
       <c r="O12" t="n">
-        <v>5.024148021356561</v>
+        <v>5.018621160598269</v>
       </c>
       <c r="P12" t="n">
-        <v>329.5073594274765</v>
+        <v>329.5271412327938</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -18822,7 +18877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M314"/>
+  <dimension ref="A1:M315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39859,6 +39914,73 @@
         </is>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>-35.55974859563062,174.48614685323082</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>-35.56010604704656,174.48693600931514</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>-35.56043855512522,174.4877382393732</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>-35.56072565189869,174.48856427096868</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>-35.560967051030765,174.48941665242793</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>-35.56118377496121,174.4903106270401</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>-35.561378761107775,174.49120518471327</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>-35.56152963486843,174.49208761449214</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>-35.56168001469915,174.4930085171265</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>-35.561673958630095,174.49394616441816</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>-35.561796951503545,174.49484863948564</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
